--- a/ekta-games-import-308.xlsx
+++ b/ekta-games-import-308.xlsx
@@ -5792,7 +5792,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>{"type":"fixed","name":"Rahul Garg &amp; Nilesh Mahtre","age":25}</t>
+          <t>{"type":"fixed","name":"Rahul Garg &amp; Nilesh Mhatre","age":25}</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
